--- a/ICP-Base/for_redistribution_files_only/Total_Oxide_Calculations/Oxides.xlsx
+++ b/ICP-Base/for_redistribution_files_only/Total_Oxide_Calculations/Oxides.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unibe365-my.sharepoint.com/personal/sebastian_stumpf_unibe_ch/Documents/PhD/ICP-Base/ICP-Base_dev/Total_Oxide_Calculations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="165" documentId="11_AD4DB114E441178AC67DF4EAB656CEA0693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85DCBB8C-0D42-4802-B31C-CCF10FE83638}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="11_C93881D2F499C0CA9E24614525B7E03D54DD654E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7009A8F-4C0B-49F2-B124-5212A6E450DF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -505,6 +505,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -514,12 +518,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -534,13 +544,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -826,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -836,7 +853,7 @@
     <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>136</v>
       </c>
@@ -853,7 +870,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -861,13 +878,15 @@
         <v>86</v>
       </c>
       <c r="C2" s="1">
-        <v>1.079</v>
+        <v>1.0742</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -875,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>1.889</v>
+        <v>1.8895</v>
       </c>
       <c r="D3" t="s">
         <v>146</v>
@@ -883,22 +902,26 @@
       <c r="E3" s="1" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="5">
         <v>1.32</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -906,13 +929,15 @@
         <v>88</v>
       </c>
       <c r="C5" s="1">
-        <v>1.2709999999999999</v>
+        <v>1.1217999999999999</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -920,13 +945,15 @@
         <v>89</v>
       </c>
       <c r="C6" s="1">
-        <v>3.22</v>
+        <v>3.2202000000000002</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -934,13 +961,15 @@
         <v>14</v>
       </c>
       <c r="C7" s="1">
-        <v>1.1160000000000001</v>
+        <v>1.1165</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -948,13 +977,15 @@
         <v>16</v>
       </c>
       <c r="C8" s="1">
-        <v>2.7850000000000001</v>
+        <v>2.7753000000000001</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -962,13 +993,15 @@
         <v>90</v>
       </c>
       <c r="C9" s="1">
-        <v>1.159</v>
+        <v>1.1148</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -984,8 +1017,10 @@
       <c r="E10" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -993,7 +1028,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="1">
-        <v>1.4</v>
+        <v>1.3992</v>
       </c>
       <c r="D11" t="s">
         <v>140</v>
@@ -1001,8 +1036,10 @@
       <c r="E11" s="1" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -1010,13 +1047,15 @@
         <v>21</v>
       </c>
       <c r="C12" s="1">
-        <v>1.143</v>
+        <v>1.1423000000000001</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -1024,13 +1063,15 @@
         <v>91</v>
       </c>
       <c r="C13" s="1">
-        <v>1.357</v>
+        <v>1.2283999999999999</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -1046,8 +1087,10 @@
       <c r="E14" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -1055,13 +1098,15 @@
         <v>24</v>
       </c>
       <c r="C15" s="1">
-        <v>1.2709999999999999</v>
+        <v>1.2715000000000001</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -1069,7 +1114,7 @@
         <v>92</v>
       </c>
       <c r="C16" s="1">
-        <v>1.462</v>
+        <v>1.4616</v>
       </c>
       <c r="D16" t="s">
         <v>150</v>
@@ -1077,22 +1122,26 @@
       <c r="E16" s="1" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="5">
         <v>1.0629999999999999</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
@@ -1100,55 +1149,63 @@
         <v>28</v>
       </c>
       <c r="C18" s="1">
-        <v>1.252</v>
+        <v>1.2518</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="5">
         <v>1.1479999999999999</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="5">
         <v>1.143</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="5">
         <v>1.1579999999999999</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
@@ -1156,7 +1213,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="2">
-        <v>1.286</v>
+        <v>1.2865</v>
       </c>
       <c r="D22" t="s">
         <v>149</v>
@@ -1164,8 +1221,10 @@
       <c r="E22" s="1" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
@@ -1173,27 +1232,31 @@
         <v>97</v>
       </c>
       <c r="C23" s="1">
-        <v>1.2849999999999999</v>
+        <v>1.3442000000000001</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="1">
-        <v>1.1519999999999999</v>
+      <c r="C24" s="4">
+        <v>1.152604887044721</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>35</v>
       </c>
@@ -1201,55 +1264,63 @@
         <v>99</v>
       </c>
       <c r="C25" s="1">
-        <v>1.43</v>
+        <v>1.4408000000000001</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="5">
         <v>1.2110000000000001</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="5">
         <v>1.1459999999999999</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="5">
         <v>1.2030000000000001</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>134</v>
       </c>
@@ -1262,8 +1333,10 @@
       <c r="E29" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
@@ -1271,7 +1344,7 @@
         <v>3</v>
       </c>
       <c r="C30" s="1">
-        <v>1.204</v>
+        <v>1.2045999999999999</v>
       </c>
       <c r="D30" t="s">
         <v>143</v>
@@ -1279,8 +1352,10 @@
       <c r="E30" s="1" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
@@ -1288,13 +1363,15 @@
         <v>103</v>
       </c>
       <c r="C31" s="1">
-        <v>1.1719999999999999</v>
+        <v>1.1728000000000001</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>41</v>
       </c>
@@ -1302,27 +1379,31 @@
         <v>104</v>
       </c>
       <c r="C32" s="1">
-        <v>1.34</v>
+        <v>2.1528999999999998</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="5">
         <v>1.137</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>43</v>
       </c>
@@ -1330,7 +1411,7 @@
         <v>44</v>
       </c>
       <c r="C34" s="1">
-        <v>1.6579999999999999</v>
+        <v>1.6583000000000001</v>
       </c>
       <c r="D34" t="s">
         <v>142</v>
@@ -1338,8 +1419,10 @@
       <c r="E34" s="1" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>45</v>
       </c>
@@ -1347,20 +1430,22 @@
         <v>132</v>
       </c>
       <c r="C35" s="2">
-        <v>1.2909999999999999</v>
+        <v>1.2911999999999999</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="5">
         <v>1.5</v>
       </c>
       <c r="D36" t="s">
@@ -1369,15 +1454,17 @@
       <c r="E36" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="5">
         <v>1.3480000000000001</v>
       </c>
       <c r="D37" t="s">
@@ -1386,36 +1473,42 @@
       <c r="E37" s="1" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C38" s="5">
         <v>1.431</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C39" s="5">
         <v>1.1659999999999999</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>50</v>
       </c>
@@ -1423,7 +1516,7 @@
         <v>51</v>
       </c>
       <c r="C40" s="1">
-        <v>1.2729999999999999</v>
+        <v>1.2726</v>
       </c>
       <c r="D40" t="s">
         <v>157</v>
@@ -1431,8 +1524,10 @@
       <c r="E40" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>52</v>
       </c>
@@ -1440,13 +1535,15 @@
         <v>109</v>
       </c>
       <c r="C41" s="1">
-        <v>2.2909999999999999</v>
+        <v>2.2913999999999999</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>53</v>
       </c>
@@ -1454,7 +1551,7 @@
         <v>54</v>
       </c>
       <c r="C42" s="1">
-        <v>1.077</v>
+        <v>1.0771999999999999</v>
       </c>
       <c r="D42" t="s">
         <v>156</v>
@@ -1462,50 +1559,58 @@
       <c r="E42" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43" s="5">
         <v>1.206</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C44" s="5">
         <v>1.208</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C45" s="1">
+      <c r="C45" s="5">
         <v>1.2130000000000001</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>59</v>
       </c>
@@ -1513,48 +1618,54 @@
         <v>112</v>
       </c>
       <c r="C46" s="1">
-        <v>1.0920000000000001</v>
+        <v>1.0935999999999999</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C47" s="5">
         <v>1.881</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C48" s="5">
         <v>1.3660000000000001</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C49" s="1">
+      <c r="C49" s="5">
         <v>2.4980000000000002</v>
       </c>
       <c r="D49" t="s">
@@ -1563,8 +1674,10 @@
       <c r="E49" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>63</v>
       </c>
@@ -1572,41 +1685,47 @@
         <v>115</v>
       </c>
       <c r="C50" s="1">
-        <v>1.53</v>
+        <v>1.1971000000000001</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C51" s="5">
         <v>1.546</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C52" s="5">
         <v>1.3660000000000001</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>66</v>
       </c>
@@ -1614,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="C53" s="1">
-        <v>2.1389999999999998</v>
+        <v>2.1393</v>
       </c>
       <c r="D53" t="s">
         <v>141</v>
@@ -1622,22 +1741,26 @@
       <c r="E53" s="1" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C54" s="1">
+      <c r="C54" s="5">
         <v>1.1599999999999999</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>68</v>
       </c>
@@ -1645,13 +1768,15 @@
         <v>119</v>
       </c>
       <c r="C55" s="1">
-        <v>1.2689999999999999</v>
+        <v>1.2695000000000001</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>69</v>
       </c>
@@ -1659,13 +1784,15 @@
         <v>70</v>
       </c>
       <c r="C56" s="1">
-        <v>1.1830000000000001</v>
+        <v>1.1826000000000001</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>71</v>
       </c>
@@ -1673,27 +1800,31 @@
         <v>120</v>
       </c>
       <c r="C57" s="1">
-        <v>1.2210000000000001</v>
+        <v>1.2211000000000001</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C58" s="1">
+      <c r="C58" s="5">
         <v>1.1759999999999999</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I58" s="3"/>
+      <c r="J58" s="3"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>73</v>
       </c>
@@ -1701,34 +1832,38 @@
         <v>122</v>
       </c>
       <c r="C59" s="1">
-        <v>1.2230000000000001</v>
+        <v>1.2507999999999999</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I59" s="3"/>
+      <c r="J59" s="3"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C60" s="1">
+      <c r="C60" s="5">
         <v>1.137</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C61" s="1">
+      <c r="C61" s="5">
         <v>1.6679999999999999</v>
       </c>
       <c r="D61" t="s">
@@ -1737,36 +1872,42 @@
       <c r="E61" s="1" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C62" s="1">
+      <c r="C62" s="5">
         <v>1.123</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C63" s="1">
+      <c r="C63" s="5">
         <v>1.1419999999999999</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>78</v>
       </c>
@@ -1774,13 +1915,15 @@
         <v>133</v>
       </c>
       <c r="C64" s="1">
-        <v>1.1339999999999999</v>
+        <v>1.1344000000000001</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>79</v>
       </c>
@@ -1788,55 +1931,63 @@
         <v>127</v>
       </c>
       <c r="C65" s="1">
-        <v>1.7849999999999999</v>
+        <v>1.7851999999999999</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C66" s="1">
+      <c r="C66" s="5">
         <v>1.2609999999999999</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C67" s="5">
         <v>1.2789999999999999</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C68" s="1">
+      <c r="C68" s="5">
         <v>1.139</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I68" s="3"/>
+      <c r="J68" s="3"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>83</v>
       </c>
@@ -1844,13 +1995,15 @@
         <v>84</v>
       </c>
       <c r="C69" s="1">
-        <v>1.2450000000000001</v>
+        <v>1.2446999999999999</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>85</v>
       </c>
@@ -1858,13 +2011,54 @@
         <v>131</v>
       </c>
       <c r="C70" s="1">
-        <v>1.35</v>
+        <v>1.3508</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>155</v>
       </c>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F72" s="3"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F73" s="3"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F74" s="3"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F75" s="3"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F76" s="3"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F77" s="3"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F78" s="3"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F79" s="3"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F80" s="3"/>
+    </row>
+    <row r="81" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F81" s="3"/>
+    </row>
+    <row r="82" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F82" s="3"/>
+    </row>
+    <row r="83" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F83" s="3"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F2:G58">
+    <sortCondition ref="F2"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>